--- a/Output/Referencias_update.xlsx
+++ b/Output/Referencias_update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eagel\OneDrive\Escritorio\Lalo\Gob\Proyectos\Infografias\Output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIGEH\Desktop\Lalo\Gob\Proyectos\Infografias\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C77A892-ED3E-4552-9B20-C70842B7EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09826FBB-0AB3-4BF1-8867-400DE13A2C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3547" uniqueCount="802">
   <si>
     <t>Categoria</t>
   </si>
@@ -2395,6 +2395,42 @@
   </si>
   <si>
     <t xml:space="preserve">Tabulados, De integración-2025-Turismo / Descargar Establecimientos de hospedaje registrados por municipio según tipo de alojamiento / Al 31 de diciembre de 2024 </t>
+  </si>
+  <si>
+    <t>Lenguas Indigenas Top 5</t>
+  </si>
+  <si>
+    <t>Lenguas Indigenas Top 5 Conteo</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada 1</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada 2</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada 3</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada 4</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada 5</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada conteo 1</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada conteo 2</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada conteo 3</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada conteo 4</t>
+  </si>
+  <si>
+    <t>Lengua Indigena más hablada conteo 5</t>
   </si>
 </sst>
 </file>
@@ -2754,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H695"/>
+  <dimension ref="A1:H707"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="129.33203125" customWidth="1"/>
@@ -16686,6 +16722,246 @@
         <v>740</v>
       </c>
       <c r="F695" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>668</v>
+      </c>
+      <c r="B696" t="s">
+        <v>790</v>
+      </c>
+      <c r="C696" t="s">
+        <v>721</v>
+      </c>
+      <c r="D696">
+        <v>2020</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F696" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>668</v>
+      </c>
+      <c r="B697" t="s">
+        <v>791</v>
+      </c>
+      <c r="C697" t="s">
+        <v>721</v>
+      </c>
+      <c r="D697">
+        <v>2020</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F697" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>668</v>
+      </c>
+      <c r="B698" t="s">
+        <v>792</v>
+      </c>
+      <c r="C698" t="s">
+        <v>721</v>
+      </c>
+      <c r="D698">
+        <v>2020</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F698" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>668</v>
+      </c>
+      <c r="B699" t="s">
+        <v>793</v>
+      </c>
+      <c r="C699" t="s">
+        <v>721</v>
+      </c>
+      <c r="D699">
+        <v>2020</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F699" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>668</v>
+      </c>
+      <c r="B700" t="s">
+        <v>794</v>
+      </c>
+      <c r="C700" t="s">
+        <v>721</v>
+      </c>
+      <c r="D700">
+        <v>2020</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F700" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>668</v>
+      </c>
+      <c r="B701" t="s">
+        <v>795</v>
+      </c>
+      <c r="C701" t="s">
+        <v>721</v>
+      </c>
+      <c r="D701">
+        <v>2020</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F701" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>668</v>
+      </c>
+      <c r="B702" t="s">
+        <v>796</v>
+      </c>
+      <c r="C702" t="s">
+        <v>721</v>
+      </c>
+      <c r="D702">
+        <v>2020</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F702" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>668</v>
+      </c>
+      <c r="B703" t="s">
+        <v>797</v>
+      </c>
+      <c r="C703" t="s">
+        <v>721</v>
+      </c>
+      <c r="D703">
+        <v>2020</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F703" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>668</v>
+      </c>
+      <c r="B704" t="s">
+        <v>798</v>
+      </c>
+      <c r="C704" t="s">
+        <v>721</v>
+      </c>
+      <c r="D704">
+        <v>2020</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F704" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>668</v>
+      </c>
+      <c r="B705" t="s">
+        <v>799</v>
+      </c>
+      <c r="C705" t="s">
+        <v>721</v>
+      </c>
+      <c r="D705">
+        <v>2020</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F705" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>668</v>
+      </c>
+      <c r="B706" t="s">
+        <v>800</v>
+      </c>
+      <c r="C706" t="s">
+        <v>721</v>
+      </c>
+      <c r="D706">
+        <v>2020</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F706" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>668</v>
+      </c>
+      <c r="B707" t="s">
+        <v>801</v>
+      </c>
+      <c r="C707" t="s">
+        <v>721</v>
+      </c>
+      <c r="D707">
+        <v>2020</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F707" t="s">
         <v>742</v>
       </c>
     </row>
@@ -16760,8 +17036,9 @@
     <hyperlink ref="E295" r:id="rId66" xr:uid="{0696C12F-8AB3-481B-9779-8FEC3986603D}"/>
     <hyperlink ref="E296" r:id="rId67" location="collapse-Tabulados" xr:uid="{939F82B4-FE77-42A2-BDF1-C94E5BEF47AE}"/>
     <hyperlink ref="E297:E315" r:id="rId68" location="collapse-Tabulados" display="https://www.inegi.org.mx/app/areasgeograficas/?ag=13#collapse-Tabulados" xr:uid="{34CB1DA4-04C3-4CA3-A7A2-DE7227652AF8}"/>
+    <hyperlink ref="E696:E707" r:id="rId69" display="https://www.inpi.gob.mx/indicadores2020/" xr:uid="{936B9A7C-1D8D-4A20-8A3E-D81C3A3049D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId70"/>
 </worksheet>
 </file>